--- a/Lab/Excel_Text_Date_Functions - assignment.xlsx
+++ b/Lab/Excel_Text_Date_Functions - assignment.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="6800" tabRatio="500" firstSheet="3" activeTab="3"/>
+    <workbookView windowWidth="19200" windowHeight="6800" tabRatio="500" firstSheet="3" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="CRM Dataset" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1336" uniqueCount="698">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1332" uniqueCount="695">
   <si>
     <t>CRM Customer Dataset  --  25 rows with intentionally messy names, emails and phones for text function practice</t>
   </si>
@@ -1142,9 +1142,6 @@
     <t>Check: has gmail</t>
   </si>
   <si>
-    <t>9743642838</t>
-  </si>
-  <si>
     <t>***@hotmail.com</t>
   </si>
   <si>
@@ -1154,13 +1151,7 @@
     <t>Not found</t>
   </si>
   <si>
-    <t>9982965198</t>
-  </si>
-  <si>
     <t>***@biz.net</t>
-  </si>
-  <si>
-    <t>9556561458</t>
   </si>
   <si>
     <t>***@gmail.com</t>
@@ -5960,7 +5951,7 @@
   <sheetData>
     <row r="1" ht="37.5" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5968,7 +5959,7 @@
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5977,7 +5968,7 @@
     <row r="3" ht="15.25"/>
     <row r="4" ht="25.5" customHeight="1" spans="1:4">
       <c r="A4" s="86" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="B4" s="86"/>
       <c r="C4" s="86"/>
@@ -5985,63 +5976,63 @@
     </row>
     <row r="5" ht="43.5" customHeight="1" spans="1:4">
       <c r="A5" s="87" t="s">
+        <v>467</v>
+      </c>
+      <c r="B5" s="88" t="s">
+        <v>468</v>
+      </c>
+      <c r="C5" s="89" t="s">
+        <v>469</v>
+      </c>
+      <c r="D5" s="90" t="s">
         <v>470</v>
-      </c>
-      <c r="B5" s="88" t="s">
-        <v>471</v>
-      </c>
-      <c r="C5" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="D5" s="90" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="6" ht="43.5" customHeight="1" spans="1:4">
       <c r="A6" s="87" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="B6" s="88" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="C6" s="89" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D6" s="90" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="7" ht="43.5" customHeight="1" spans="1:4">
       <c r="A7" s="91" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="B7" s="88" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="C7" s="89" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D7" s="92" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="8" ht="43.5" customHeight="1" spans="1:4">
       <c r="A8" s="91" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="B8" s="88" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="C8" s="89" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D8" s="92" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="9" ht="25.5" customHeight="1" spans="1:4">
       <c r="A9" s="86" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="B9" s="86"/>
       <c r="C9" s="86"/>
@@ -6049,49 +6040,49 @@
     </row>
     <row r="10" ht="43.5" customHeight="1" spans="1:4">
       <c r="A10" s="87" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B10" s="88" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="C10" s="89" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D10" s="90" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="11" ht="43.5" customHeight="1" spans="1:4">
       <c r="A11" s="87" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="B11" s="88" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="C11" s="89" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D11" s="90" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="12" ht="43.5" customHeight="1" spans="1:4">
       <c r="A12" s="91" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B12" s="88" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C12" s="89" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D12" s="92" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="13" ht="25.5" customHeight="1" spans="1:4">
       <c r="A13" s="86" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B13" s="86"/>
       <c r="C13" s="86"/>
@@ -6099,49 +6090,49 @@
     </row>
     <row r="14" ht="43.5" customHeight="1" spans="1:4">
       <c r="A14" s="87" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="B14" s="88" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C14" s="89" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D14" s="90" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="15" ht="43.5" customHeight="1" spans="1:4">
       <c r="A15" s="91" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="B15" s="88" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C15" s="89" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D15" s="92" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="16" ht="43.5" customHeight="1" spans="1:4">
       <c r="A16" s="91" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B16" s="88" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="C16" s="89" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D16" s="92" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="17" ht="25.5" customHeight="1" spans="1:4">
       <c r="A17" s="86" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="B17" s="86"/>
       <c r="C17" s="86"/>
@@ -6149,63 +6140,63 @@
     </row>
     <row r="18" ht="43.5" customHeight="1" spans="1:4">
       <c r="A18" s="87" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="B18" s="88" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="C18" s="89" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D18" s="90" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="19" ht="43.5" customHeight="1" spans="1:4">
       <c r="A19" s="87" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B19" s="88" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="C19" s="89" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D19" s="90" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="20" ht="43.5" customHeight="1" spans="1:4">
       <c r="A20" s="91" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="B20" s="88" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="C20" s="89" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D20" s="92" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="21" ht="43.5" customHeight="1" spans="1:4">
       <c r="A21" s="91" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="B21" s="88" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="C21" s="89" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D21" s="92" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="22" ht="25.5" customHeight="1" spans="1:4">
       <c r="A22" s="86" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="B22" s="86"/>
       <c r="C22" s="86"/>
@@ -6213,49 +6204,49 @@
     </row>
     <row r="23" ht="43.5" customHeight="1" spans="1:4">
       <c r="A23" s="87" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="B23" s="88" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="C23" s="89" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D23" s="90" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="24" ht="43.5" customHeight="1" spans="1:4">
       <c r="A24" s="87" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="B24" s="88" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="C24" s="89" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D24" s="90" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="25" ht="43.5" customHeight="1" spans="1:4">
       <c r="A25" s="87" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="B25" s="88" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="C25" s="89" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D25" s="90" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="26" ht="25.5" customHeight="1" spans="1:4">
       <c r="A26" s="86" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="B26" s="86"/>
       <c r="C26" s="86"/>
@@ -6263,49 +6254,49 @@
     </row>
     <row r="27" ht="43.5" customHeight="1" spans="1:4">
       <c r="A27" s="87" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="B27" s="88" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="C27" s="89" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D27" s="90" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="28" ht="43.5" customHeight="1" spans="1:4">
       <c r="A28" s="91" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="B28" s="88" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="C28" s="89" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D28" s="92" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="29" ht="43.5" customHeight="1" spans="1:4">
       <c r="A29" s="87" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="B29" s="88" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="C29" s="89" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D29" s="90" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="30" ht="25.5" customHeight="1" spans="1:4">
       <c r="A30" s="86" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B30" s="86"/>
       <c r="C30" s="86"/>
@@ -6313,49 +6304,49 @@
     </row>
     <row r="31" ht="43.5" customHeight="1" spans="1:4">
       <c r="A31" s="91" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="B31" s="88" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C31" s="89" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D31" s="92" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="32" ht="43.5" customHeight="1" spans="1:4">
       <c r="A32" s="91" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="B32" s="88" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="C32" s="89" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D32" s="92" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="33" ht="43.5" customHeight="1" spans="1:4">
       <c r="A33" s="87" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="B33" s="88" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="C33" s="89" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D33" s="90" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="34" ht="25.5" customHeight="1" spans="1:4">
       <c r="A34" s="86" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="B34" s="86"/>
       <c r="C34" s="86"/>
@@ -6363,30 +6354,30 @@
     </row>
     <row r="35" ht="43.5" customHeight="1" spans="1:4">
       <c r="A35" s="91" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B35" s="88" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="C35" s="89" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D35" s="92" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="36" ht="43.5" customHeight="1" spans="1:4">
       <c r="A36" s="93" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="B36" s="88" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="C36" s="89" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D36" s="94" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
     </row>
   </sheetData>
@@ -6418,7 +6409,7 @@
   <sheetData>
     <row r="1" ht="37.5" customHeight="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6428,7 +6419,7 @@
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -6438,82 +6429,82 @@
     </row>
     <row r="3" ht="21.75" customHeight="1" spans="1:6">
       <c r="A3" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>533</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>534</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>535</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>536</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>537</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="4" ht="31.5" customHeight="1" spans="1:6">
       <c r="A4" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>537</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>538</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>539</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>540</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="F4" s="8" t="s">
         <v>541</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>542</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>543</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="5" ht="31.5" customHeight="1" spans="1:6">
       <c r="A5" s="9" t="s">
+        <v>542</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>543</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>544</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>539</v>
+      </c>
+      <c r="E5" s="11" t="s">
         <v>545</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="F5" s="13" t="s">
         <v>546</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>547</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>542</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>548</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="6" ht="31.5" customHeight="1" spans="1:6">
       <c r="A6" s="4" t="s">
+        <v>547</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>548</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>549</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>539</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>550</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="F6" s="8" t="s">
         <v>551</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>552</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>542</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>553</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="7" ht="31.5" customHeight="1" spans="1:6">
@@ -6521,19 +6512,19 @@
         <v>180</v>
       </c>
       <c r="B7" s="10" t="s">
+        <v>552</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>553</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>539</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>554</v>
+      </c>
+      <c r="F7" s="13" t="s">
         <v>555</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>556</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>542</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>557</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="8" ht="31.5" customHeight="1" spans="1:6">
@@ -6541,19 +6532,19 @@
         <v>217</v>
       </c>
       <c r="B8" s="15" t="s">
+        <v>556</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>557</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>539</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>558</v>
+      </c>
+      <c r="F8" s="18" t="s">
         <v>559</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>560</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>542</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>561</v>
-      </c>
-      <c r="F8" s="18" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="9" ht="31.5" customHeight="1" spans="1:6">
@@ -6561,19 +6552,19 @@
         <v>218</v>
       </c>
       <c r="B9" s="20" t="s">
+        <v>560</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>561</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>539</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>562</v>
+      </c>
+      <c r="F9" s="23" t="s">
         <v>563</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>564</v>
-      </c>
-      <c r="D9" s="22" t="s">
-        <v>542</v>
-      </c>
-      <c r="E9" s="21" t="s">
-        <v>565</v>
-      </c>
-      <c r="F9" s="23" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="10" ht="31.5" customHeight="1" spans="1:6">
@@ -6581,579 +6572,579 @@
         <v>219</v>
       </c>
       <c r="B10" s="15" t="s">
+        <v>564</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>565</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>539</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>566</v>
+      </c>
+      <c r="F10" s="18" t="s">
         <v>567</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>568</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>542</v>
-      </c>
-      <c r="E10" s="16" t="s">
-        <v>569</v>
-      </c>
-      <c r="F10" s="18" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="11" ht="31.5" customHeight="1" spans="1:6">
       <c r="A11" s="19" t="s">
+        <v>568</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>569</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>570</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>539</v>
+      </c>
+      <c r="E11" s="21" t="s">
         <v>571</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="F11" s="23" t="s">
         <v>572</v>
-      </c>
-      <c r="C11" s="21" t="s">
-        <v>573</v>
-      </c>
-      <c r="D11" s="22" t="s">
-        <v>542</v>
-      </c>
-      <c r="E11" s="21" t="s">
-        <v>574</v>
-      </c>
-      <c r="F11" s="23" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="12" ht="31.5" customHeight="1" spans="1:6">
       <c r="A12" s="14" t="s">
+        <v>573</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>574</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>575</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>539</v>
+      </c>
+      <c r="E12" s="16" t="s">
         <v>576</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="F12" s="18" t="s">
         <v>577</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>578</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>542</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>579</v>
-      </c>
-      <c r="F12" s="18" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="13" ht="31.5" customHeight="1" spans="1:6">
       <c r="A13" s="24" t="s">
+        <v>578</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>579</v>
+      </c>
+      <c r="C13" s="26" t="s">
+        <v>580</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>539</v>
+      </c>
+      <c r="E13" s="26" t="s">
         <v>581</v>
       </c>
-      <c r="B13" s="25" t="s">
+      <c r="F13" s="28" t="s">
         <v>582</v>
-      </c>
-      <c r="C13" s="26" t="s">
-        <v>583</v>
-      </c>
-      <c r="D13" s="27" t="s">
-        <v>542</v>
-      </c>
-      <c r="E13" s="26" t="s">
-        <v>584</v>
-      </c>
-      <c r="F13" s="28" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="14" ht="31.5" customHeight="1" spans="1:6">
       <c r="A14" s="29" t="s">
+        <v>583</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>584</v>
+      </c>
+      <c r="C14" s="31" t="s">
+        <v>585</v>
+      </c>
+      <c r="D14" s="32" t="s">
+        <v>539</v>
+      </c>
+      <c r="E14" s="31" t="s">
         <v>586</v>
       </c>
-      <c r="B14" s="30" t="s">
+      <c r="F14" s="33" t="s">
         <v>587</v>
-      </c>
-      <c r="C14" s="31" t="s">
-        <v>588</v>
-      </c>
-      <c r="D14" s="32" t="s">
-        <v>542</v>
-      </c>
-      <c r="E14" s="31" t="s">
-        <v>589</v>
-      </c>
-      <c r="F14" s="33" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="15" ht="31.5" customHeight="1" spans="1:6">
       <c r="A15" s="24" t="s">
+        <v>588</v>
+      </c>
+      <c r="B15" s="25" t="s">
+        <v>589</v>
+      </c>
+      <c r="C15" s="26" t="s">
+        <v>590</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>539</v>
+      </c>
+      <c r="E15" s="26" t="s">
         <v>591</v>
       </c>
-      <c r="B15" s="25" t="s">
+      <c r="F15" s="28" t="s">
         <v>592</v>
-      </c>
-      <c r="C15" s="26" t="s">
-        <v>593</v>
-      </c>
-      <c r="D15" s="27" t="s">
-        <v>542</v>
-      </c>
-      <c r="E15" s="26" t="s">
-        <v>594</v>
-      </c>
-      <c r="F15" s="28" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="16" ht="31.5" customHeight="1" spans="1:6">
       <c r="A16" s="29" t="s">
+        <v>593</v>
+      </c>
+      <c r="B16" s="30" t="s">
+        <v>594</v>
+      </c>
+      <c r="C16" s="31" t="s">
+        <v>595</v>
+      </c>
+      <c r="D16" s="32" t="s">
+        <v>539</v>
+      </c>
+      <c r="E16" s="31" t="s">
         <v>596</v>
       </c>
-      <c r="B16" s="30" t="s">
+      <c r="F16" s="33" t="s">
         <v>597</v>
-      </c>
-      <c r="C16" s="31" t="s">
-        <v>598</v>
-      </c>
-      <c r="D16" s="32" t="s">
-        <v>542</v>
-      </c>
-      <c r="E16" s="31" t="s">
-        <v>599</v>
-      </c>
-      <c r="F16" s="33" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="17" ht="31.5" customHeight="1" spans="1:6">
       <c r="A17" s="34" t="s">
+        <v>598</v>
+      </c>
+      <c r="B17" s="35" t="s">
+        <v>599</v>
+      </c>
+      <c r="C17" s="36" t="s">
+        <v>600</v>
+      </c>
+      <c r="D17" s="37" t="s">
+        <v>539</v>
+      </c>
+      <c r="E17" s="36" t="s">
         <v>601</v>
       </c>
-      <c r="B17" s="35" t="s">
+      <c r="F17" s="38" t="s">
         <v>602</v>
-      </c>
-      <c r="C17" s="36" t="s">
-        <v>603</v>
-      </c>
-      <c r="D17" s="37" t="s">
-        <v>542</v>
-      </c>
-      <c r="E17" s="36" t="s">
-        <v>604</v>
-      </c>
-      <c r="F17" s="38" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="18" ht="31.5" customHeight="1" spans="1:6">
       <c r="A18" s="39" t="s">
+        <v>603</v>
+      </c>
+      <c r="B18" s="40" t="s">
+        <v>604</v>
+      </c>
+      <c r="C18" s="41" t="s">
+        <v>605</v>
+      </c>
+      <c r="D18" s="42" t="s">
+        <v>539</v>
+      </c>
+      <c r="E18" s="41" t="s">
         <v>606</v>
       </c>
-      <c r="B18" s="40" t="s">
+      <c r="F18" s="43" t="s">
         <v>607</v>
-      </c>
-      <c r="C18" s="41" t="s">
-        <v>608</v>
-      </c>
-      <c r="D18" s="42" t="s">
-        <v>542</v>
-      </c>
-      <c r="E18" s="41" t="s">
-        <v>609</v>
-      </c>
-      <c r="F18" s="43" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="19" ht="31.5" customHeight="1" spans="1:6">
       <c r="A19" s="34" t="s">
+        <v>608</v>
+      </c>
+      <c r="B19" s="35" t="s">
+        <v>609</v>
+      </c>
+      <c r="C19" s="36" t="s">
+        <v>610</v>
+      </c>
+      <c r="D19" s="37" t="s">
+        <v>539</v>
+      </c>
+      <c r="E19" s="36" t="s">
         <v>611</v>
       </c>
-      <c r="B19" s="35" t="s">
+      <c r="F19" s="38" t="s">
         <v>612</v>
-      </c>
-      <c r="C19" s="36" t="s">
-        <v>613</v>
-      </c>
-      <c r="D19" s="37" t="s">
-        <v>542</v>
-      </c>
-      <c r="E19" s="36" t="s">
-        <v>614</v>
-      </c>
-      <c r="F19" s="38" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="20" ht="31.5" customHeight="1" spans="1:6">
       <c r="A20" s="39" t="s">
+        <v>613</v>
+      </c>
+      <c r="B20" s="40" t="s">
+        <v>614</v>
+      </c>
+      <c r="C20" s="41" t="s">
+        <v>615</v>
+      </c>
+      <c r="D20" s="42" t="s">
+        <v>539</v>
+      </c>
+      <c r="E20" s="41" t="s">
         <v>616</v>
       </c>
-      <c r="B20" s="40" t="s">
+      <c r="F20" s="43" t="s">
         <v>617</v>
-      </c>
-      <c r="C20" s="41" t="s">
-        <v>618</v>
-      </c>
-      <c r="D20" s="42" t="s">
-        <v>542</v>
-      </c>
-      <c r="E20" s="41" t="s">
-        <v>619</v>
-      </c>
-      <c r="F20" s="43" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="21" ht="31.5" customHeight="1" spans="1:6">
       <c r="A21" s="44" t="s">
+        <v>618</v>
+      </c>
+      <c r="B21" s="45" t="s">
+        <v>372</v>
+      </c>
+      <c r="C21" s="46" t="s">
+        <v>619</v>
+      </c>
+      <c r="D21" s="47" t="s">
+        <v>620</v>
+      </c>
+      <c r="E21" s="46" t="s">
         <v>621</v>
       </c>
-      <c r="B21" s="45" t="s">
-        <v>375</v>
-      </c>
-      <c r="C21" s="46" t="s">
+      <c r="F21" s="48" t="s">
         <v>622</v>
-      </c>
-      <c r="D21" s="47" t="s">
-        <v>623</v>
-      </c>
-      <c r="E21" s="46" t="s">
-        <v>624</v>
-      </c>
-      <c r="F21" s="48" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="22" ht="31.5" customHeight="1" spans="1:6">
       <c r="A22" s="49" t="s">
+        <v>623</v>
+      </c>
+      <c r="B22" s="50" t="s">
+        <v>374</v>
+      </c>
+      <c r="C22" s="51" t="s">
+        <v>624</v>
+      </c>
+      <c r="D22" s="52" t="s">
+        <v>620</v>
+      </c>
+      <c r="E22" s="51" t="s">
+        <v>625</v>
+      </c>
+      <c r="F22" s="53" t="s">
         <v>626</v>
-      </c>
-      <c r="B22" s="50" t="s">
-        <v>377</v>
-      </c>
-      <c r="C22" s="51" t="s">
-        <v>627</v>
-      </c>
-      <c r="D22" s="52" t="s">
-        <v>623</v>
-      </c>
-      <c r="E22" s="51" t="s">
-        <v>628</v>
-      </c>
-      <c r="F22" s="53" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="23" ht="31.5" customHeight="1" spans="1:6">
       <c r="A23" s="44" t="s">
+        <v>627</v>
+      </c>
+      <c r="B23" s="54" t="s">
+        <v>628</v>
+      </c>
+      <c r="C23" s="46" t="s">
+        <v>629</v>
+      </c>
+      <c r="D23" s="47" t="s">
+        <v>620</v>
+      </c>
+      <c r="E23" s="46" t="s">
         <v>630</v>
       </c>
-      <c r="B23" s="54" t="s">
+      <c r="F23" s="48" t="s">
         <v>631</v>
-      </c>
-      <c r="C23" s="46" t="s">
-        <v>632</v>
-      </c>
-      <c r="D23" s="47" t="s">
-        <v>623</v>
-      </c>
-      <c r="E23" s="46" t="s">
-        <v>633</v>
-      </c>
-      <c r="F23" s="48" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="24" ht="31.5" customHeight="1" spans="1:6">
       <c r="A24" s="49" t="s">
+        <v>632</v>
+      </c>
+      <c r="B24" s="55" t="s">
+        <v>633</v>
+      </c>
+      <c r="C24" s="51" t="s">
+        <v>634</v>
+      </c>
+      <c r="D24" s="52" t="s">
+        <v>620</v>
+      </c>
+      <c r="E24" s="51" t="s">
         <v>635</v>
       </c>
-      <c r="B24" s="55" t="s">
+      <c r="F24" s="53" t="s">
         <v>636</v>
-      </c>
-      <c r="C24" s="51" t="s">
-        <v>637</v>
-      </c>
-      <c r="D24" s="52" t="s">
-        <v>623</v>
-      </c>
-      <c r="E24" s="51" t="s">
-        <v>638</v>
-      </c>
-      <c r="F24" s="53" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="25" ht="31.5" customHeight="1" spans="1:6">
       <c r="A25" s="56" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B25" s="57" t="s">
+        <v>637</v>
+      </c>
+      <c r="C25" s="58" t="s">
+        <v>638</v>
+      </c>
+      <c r="D25" s="59" t="s">
+        <v>620</v>
+      </c>
+      <c r="E25" s="58" t="s">
+        <v>639</v>
+      </c>
+      <c r="F25" s="60" t="s">
         <v>640</v>
-      </c>
-      <c r="C25" s="58" t="s">
-        <v>641</v>
-      </c>
-      <c r="D25" s="59" t="s">
-        <v>623</v>
-      </c>
-      <c r="E25" s="58" t="s">
-        <v>642</v>
-      </c>
-      <c r="F25" s="60" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="26" ht="31.5" customHeight="1" spans="1:6">
       <c r="A26" s="61" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="B26" s="62" t="s">
+        <v>641</v>
+      </c>
+      <c r="C26" s="63" t="s">
+        <v>642</v>
+      </c>
+      <c r="D26" s="64" t="s">
+        <v>620</v>
+      </c>
+      <c r="E26" s="63" t="s">
+        <v>643</v>
+      </c>
+      <c r="F26" s="65" t="s">
         <v>644</v>
-      </c>
-      <c r="C26" s="63" t="s">
-        <v>645</v>
-      </c>
-      <c r="D26" s="64" t="s">
-        <v>623</v>
-      </c>
-      <c r="E26" s="63" t="s">
-        <v>646</v>
-      </c>
-      <c r="F26" s="65" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="27" ht="31.5" customHeight="1" spans="1:6">
       <c r="A27" s="56" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B27" s="57" t="s">
+        <v>645</v>
+      </c>
+      <c r="C27" s="58" t="s">
+        <v>646</v>
+      </c>
+      <c r="D27" s="59" t="s">
+        <v>620</v>
+      </c>
+      <c r="E27" s="58" t="s">
+        <v>647</v>
+      </c>
+      <c r="F27" s="60" t="s">
         <v>648</v>
-      </c>
-      <c r="C27" s="58" t="s">
-        <v>649</v>
-      </c>
-      <c r="D27" s="59" t="s">
-        <v>623</v>
-      </c>
-      <c r="E27" s="58" t="s">
-        <v>650</v>
-      </c>
-      <c r="F27" s="60" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="28" ht="31.5" customHeight="1" spans="1:6">
       <c r="A28" s="61" t="s">
+        <v>649</v>
+      </c>
+      <c r="B28" s="62" t="s">
+        <v>650</v>
+      </c>
+      <c r="C28" s="63" t="s">
+        <v>651</v>
+      </c>
+      <c r="D28" s="64" t="s">
+        <v>620</v>
+      </c>
+      <c r="E28" s="63" t="s">
         <v>652</v>
       </c>
-      <c r="B28" s="62" t="s">
+      <c r="F28" s="65" t="s">
         <v>653</v>
-      </c>
-      <c r="C28" s="63" t="s">
-        <v>654</v>
-      </c>
-      <c r="D28" s="64" t="s">
-        <v>623</v>
-      </c>
-      <c r="E28" s="63" t="s">
-        <v>655</v>
-      </c>
-      <c r="F28" s="65" t="s">
-        <v>656</v>
       </c>
     </row>
     <row r="29" ht="31.5" customHeight="1" spans="1:6">
       <c r="A29" s="56" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B29" s="57" t="s">
+        <v>654</v>
+      </c>
+      <c r="C29" s="58" t="s">
+        <v>655</v>
+      </c>
+      <c r="D29" s="59" t="s">
+        <v>620</v>
+      </c>
+      <c r="E29" s="58" t="s">
+        <v>656</v>
+      </c>
+      <c r="F29" s="60" t="s">
         <v>657</v>
-      </c>
-      <c r="C29" s="58" t="s">
-        <v>658</v>
-      </c>
-      <c r="D29" s="59" t="s">
-        <v>623</v>
-      </c>
-      <c r="E29" s="58" t="s">
-        <v>659</v>
-      </c>
-      <c r="F29" s="60" t="s">
-        <v>660</v>
       </c>
     </row>
     <row r="30" ht="31.5" customHeight="1" spans="1:6">
       <c r="A30" s="66" t="s">
+        <v>658</v>
+      </c>
+      <c r="B30" s="67" t="s">
+        <v>659</v>
+      </c>
+      <c r="C30" s="68" t="s">
+        <v>660</v>
+      </c>
+      <c r="D30" s="69" t="s">
+        <v>620</v>
+      </c>
+      <c r="E30" s="68" t="s">
         <v>661</v>
       </c>
-      <c r="B30" s="67" t="s">
+      <c r="F30" s="70" t="s">
         <v>662</v>
-      </c>
-      <c r="C30" s="68" t="s">
-        <v>663</v>
-      </c>
-      <c r="D30" s="69" t="s">
-        <v>623</v>
-      </c>
-      <c r="E30" s="68" t="s">
-        <v>664</v>
-      </c>
-      <c r="F30" s="70" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="31" ht="31.5" customHeight="1" spans="1:6">
       <c r="A31" s="71" t="s">
+        <v>663</v>
+      </c>
+      <c r="B31" s="72" t="s">
+        <v>664</v>
+      </c>
+      <c r="C31" s="73" t="s">
+        <v>665</v>
+      </c>
+      <c r="D31" s="74" t="s">
+        <v>620</v>
+      </c>
+      <c r="E31" s="73" t="s">
         <v>666</v>
       </c>
-      <c r="B31" s="72" t="s">
+      <c r="F31" s="75" t="s">
         <v>667</v>
-      </c>
-      <c r="C31" s="73" t="s">
-        <v>668</v>
-      </c>
-      <c r="D31" s="74" t="s">
-        <v>623</v>
-      </c>
-      <c r="E31" s="73" t="s">
-        <v>669</v>
-      </c>
-      <c r="F31" s="75" t="s">
-        <v>670</v>
       </c>
     </row>
     <row r="32" ht="31.5" customHeight="1" spans="1:6">
       <c r="A32" s="66" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="B32" s="67" t="s">
+        <v>668</v>
+      </c>
+      <c r="C32" s="68" t="s">
+        <v>669</v>
+      </c>
+      <c r="D32" s="69" t="s">
+        <v>620</v>
+      </c>
+      <c r="E32" s="68" t="s">
+        <v>670</v>
+      </c>
+      <c r="F32" s="70" t="s">
         <v>671</v>
-      </c>
-      <c r="C32" s="68" t="s">
-        <v>672</v>
-      </c>
-      <c r="D32" s="69" t="s">
-        <v>623</v>
-      </c>
-      <c r="E32" s="68" t="s">
-        <v>673</v>
-      </c>
-      <c r="F32" s="70" t="s">
-        <v>674</v>
       </c>
     </row>
     <row r="33" ht="31.5" customHeight="1" spans="1:6">
       <c r="A33" s="71" t="s">
+        <v>672</v>
+      </c>
+      <c r="B33" s="72" t="s">
+        <v>673</v>
+      </c>
+      <c r="C33" s="73" t="s">
+        <v>674</v>
+      </c>
+      <c r="D33" s="74" t="s">
+        <v>620</v>
+      </c>
+      <c r="E33" s="73" t="s">
         <v>675</v>
       </c>
-      <c r="B33" s="72" t="s">
+      <c r="F33" s="75" t="s">
         <v>676</v>
-      </c>
-      <c r="C33" s="73" t="s">
-        <v>677</v>
-      </c>
-      <c r="D33" s="74" t="s">
-        <v>623</v>
-      </c>
-      <c r="E33" s="73" t="s">
-        <v>678</v>
-      </c>
-      <c r="F33" s="75" t="s">
-        <v>679</v>
       </c>
     </row>
     <row r="34" ht="31.5" customHeight="1" spans="1:6">
       <c r="A34" s="66" t="s">
+        <v>677</v>
+      </c>
+      <c r="B34" s="67" t="s">
+        <v>678</v>
+      </c>
+      <c r="C34" s="68" t="s">
+        <v>679</v>
+      </c>
+      <c r="D34" s="69" t="s">
+        <v>620</v>
+      </c>
+      <c r="E34" s="68" t="s">
         <v>680</v>
       </c>
-      <c r="B34" s="67" t="s">
+      <c r="F34" s="70" t="s">
         <v>681</v>
-      </c>
-      <c r="C34" s="68" t="s">
-        <v>682</v>
-      </c>
-      <c r="D34" s="69" t="s">
-        <v>623</v>
-      </c>
-      <c r="E34" s="68" t="s">
-        <v>683</v>
-      </c>
-      <c r="F34" s="70" t="s">
-        <v>684</v>
       </c>
     </row>
     <row r="35" ht="31.5" customHeight="1" spans="1:6">
       <c r="A35" s="76" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="B35" s="77" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C35" s="78" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D35" s="79" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="E35" s="78" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="F35" s="80" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
     </row>
     <row r="36" ht="31.5" customHeight="1" spans="1:6">
       <c r="A36" s="81" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="B36" s="82" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C36" s="83" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="D36" s="84" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="E36" s="83" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="F36" s="85" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
     </row>
     <row r="37" ht="31.5" customHeight="1" spans="1:6">
       <c r="A37" s="76" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="B37" s="77" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C37" s="78" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="D37" s="79" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="E37" s="78" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="F37" s="80" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
     </row>
     <row r="38" ht="31.5" customHeight="1" spans="1:6">
       <c r="A38" s="81" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="B38" s="82" t="s">
+        <v>691</v>
+      </c>
+      <c r="C38" s="83" t="s">
+        <v>692</v>
+      </c>
+      <c r="D38" s="84" t="s">
+        <v>620</v>
+      </c>
+      <c r="E38" s="83" t="s">
+        <v>693</v>
+      </c>
+      <c r="F38" s="85" t="s">
         <v>694</v>
-      </c>
-      <c r="C38" s="83" t="s">
-        <v>695</v>
-      </c>
-      <c r="D38" s="84" t="s">
-        <v>623</v>
-      </c>
-      <c r="E38" s="83" t="s">
-        <v>696</v>
-      </c>
-      <c r="F38" s="85" t="s">
-        <v>697</v>
       </c>
     </row>
   </sheetData>
@@ -9076,14 +9067,15 @@
       <c r="E4" s="149">
         <v>22</v>
       </c>
-      <c r="F4" s="150" t="s">
+      <c r="F4" s="150" t="str">
+        <f>TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4,"+91",""),"-",""),"(",""),")","")," ",""))</f>
+        <v>9743642838</v>
+      </c>
+      <c r="G4" s="150" t="s">
         <v>261</v>
       </c>
-      <c r="G4" s="150" t="s">
+      <c r="H4" s="149" t="s">
         <v>262</v>
-      </c>
-      <c r="H4" s="149" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" spans="1:11">
@@ -9100,16 +9092,17 @@
         <v>10</v>
       </c>
       <c r="E5" s="151" t="s">
+        <v>263</v>
+      </c>
+      <c r="F5" s="150" t="str">
+        <f t="shared" ref="F5:F28" si="0">TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5,"+91",""),"-",""),"(",""),")","")," ",""))</f>
+        <v>9982965198</v>
+      </c>
+      <c r="G5" s="152" t="s">
         <v>264</v>
       </c>
-      <c r="F5" s="152" t="s">
-        <v>265</v>
-      </c>
-      <c r="G5" s="152" t="s">
-        <v>266</v>
-      </c>
       <c r="H5" s="151" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" spans="1:11">
@@ -9128,14 +9121,15 @@
       <c r="E6" s="149">
         <v>18</v>
       </c>
-      <c r="F6" s="150" t="s">
-        <v>267</v>
+      <c r="F6" s="150" t="str">
+        <f t="shared" si="0"/>
+        <v>9556561458</v>
       </c>
       <c r="G6" s="150" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="H6" s="149" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="1:11">
@@ -9154,20 +9148,21 @@
       <c r="E7" s="151">
         <v>20</v>
       </c>
-      <c r="F7" s="152" t="s">
-        <v>48</v>
+      <c r="F7" s="150" t="str">
+        <f t="shared" si="0"/>
+        <v>9739324688</v>
       </c>
       <c r="G7" s="152" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="H7" s="151" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="J7" s="148" t="s">
         <v>256</v>
       </c>
       <c r="K7" s="153" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" spans="1:11">
@@ -9189,7 +9184,7 @@
         <v>Not found</v>
       </c>
       <c r="F8" s="150" t="str">
-        <f>_wpsfn.SUBSTITUTES(RIGHT(B8,11),"-")</f>
+        <f t="shared" si="0"/>
         <v>9762918409</v>
       </c>
       <c r="G8" s="150" t="str">
@@ -9197,10 +9192,10 @@
         <v>  ***@company.io  </v>
       </c>
       <c r="H8" s="149" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="K8" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" spans="1:11">
@@ -9214,19 +9209,19 @@
         <v>62</v>
       </c>
       <c r="D9" s="149">
-        <f t="shared" ref="D9:D28" si="0">IFERROR(FIND("@",TRIM(C9)),"Not Found")</f>
+        <f t="shared" ref="D9:D28" si="1">IFERROR(FIND("@",TRIM(C9)),"Not Found")</f>
         <v>10</v>
       </c>
       <c r="E9" s="149">
-        <f t="shared" ref="E9:E28" si="1">IFERROR(SEARCH(".com",TRIM(C9)),"Not found")</f>
+        <f t="shared" ref="E9:E28" si="2">IFERROR(SEARCH(".com",TRIM(C9)),"Not found")</f>
         <v>18</v>
       </c>
       <c r="F9" s="150" t="str">
-        <f>_wpsfn.SUBSTITUTES(RIGHT(B9,11),"-")</f>
+        <f t="shared" si="0"/>
         <v>9159933789</v>
       </c>
       <c r="G9" s="150" t="str">
-        <f t="shared" ref="G9:G28" si="2">SUBSTITUTE(C9,LEFT(TRIM(C9),9),"***")</f>
+        <f t="shared" ref="G9:G28" si="3">SUBSTITUTE(C9,LEFT(TRIM(C9),9),"***")</f>
         <v>  ***@webmail.com  </v>
       </c>
       <c r="H9" s="151"/>
@@ -9242,16 +9237,19 @@
         <v>72</v>
       </c>
       <c r="D10" s="149">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="E10" s="149">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+      <c r="F10" s="150" t="str">
         <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="E10" s="149">
-        <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-      <c r="F10" s="150"/>
+        <v>9702332368</v>
+      </c>
       <c r="G10" s="150" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>  ***@hotmail.com  </v>
       </c>
       <c r="H10" s="149"/>
@@ -9259,7 +9257,7 @@
         <v>257</v>
       </c>
       <c r="K10" s="153" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" spans="1:11">
@@ -9270,27 +9268,27 @@
         <v>82</v>
       </c>
       <c r="C11" s="154" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="D11" s="149" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Found</v>
+      </c>
+      <c r="E11" s="149" t="str">
+        <f t="shared" si="2"/>
+        <v>Not found</v>
+      </c>
+      <c r="F11" s="150" t="str">
         <f t="shared" si="0"/>
-        <v>Not Found</v>
-      </c>
-      <c r="E11" s="149" t="str">
-        <f t="shared" si="1"/>
-        <v>Not found</v>
-      </c>
-      <c r="F11" s="152" t="str">
-        <f>_wpsfn.SUBSTITUTES(RIGHT(B11,11),"-")</f>
         <v>9461586830</v>
       </c>
       <c r="G11" s="150" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>  ***is#corp.in  </v>
       </c>
       <c r="H11" s="151"/>
       <c r="K11" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1" spans="1:11">
@@ -9304,19 +9302,19 @@
         <v>87</v>
       </c>
       <c r="D12" s="149">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="E12" s="149">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="F12" s="150" t="str">
         <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="E12" s="149">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="F12" s="152" t="str">
-        <f>_wpsfn.SUBSTITUTES(RIGHT(B12,11),"-")</f>
         <v>9801543876</v>
       </c>
       <c r="G12" s="150" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>  ***in@hotmail.com  </v>
       </c>
       <c r="H12" s="149"/>
@@ -9332,16 +9330,19 @@
         <v>94</v>
       </c>
       <c r="D13" s="149">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="E13" s="149" t="str">
+        <f t="shared" si="2"/>
+        <v>Not found</v>
+      </c>
+      <c r="F13" s="150" t="str">
         <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="E13" s="149" t="str">
-        <f t="shared" si="1"/>
-        <v>Not found</v>
-      </c>
-      <c r="F13" s="152"/>
+        <v>9835306774</v>
+      </c>
       <c r="G13" s="150" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>  ***on@company.io  </v>
       </c>
       <c r="H13" s="151"/>
@@ -9349,7 +9350,7 @@
         <v>260</v>
       </c>
       <c r="K13" s="153" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" spans="1:11">
@@ -9363,24 +9364,24 @@
         <v>99</v>
       </c>
       <c r="D14" s="149">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="E14" s="149">
+        <f t="shared" si="2"/>
+        <v>21</v>
+      </c>
+      <c r="F14" s="150" t="str">
         <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="E14" s="149">
-        <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-      <c r="F14" s="150" t="str">
-        <f>_wpsfn.SUBSTITUTES(RIGHT(B15,11),"-")</f>
-        <v>9103885085</v>
+        <v>9308812623</v>
       </c>
       <c r="G14" s="150" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>  ***lor@webmail.com  </v>
       </c>
       <c r="H14" s="149"/>
       <c r="K14" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" spans="1:11">
@@ -9391,22 +9392,22 @@
         <v>106</v>
       </c>
       <c r="C15" s="154" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D15" s="149" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Found</v>
+      </c>
+      <c r="E15" s="149" t="str">
+        <f t="shared" si="2"/>
+        <v>Not found</v>
+      </c>
+      <c r="F15" s="150" t="str">
         <f t="shared" si="0"/>
-        <v>Not Found</v>
-      </c>
-      <c r="E15" s="149" t="str">
-        <f t="shared" si="1"/>
-        <v>Not found</v>
-      </c>
-      <c r="F15" s="150" t="str">
-        <f t="shared" ref="F15:F22" si="3">_wpsfn.SUBSTITUTES(RIGHT(B16,11),"-")</f>
-        <v>9315053957</v>
+        <v>9103885085</v>
       </c>
       <c r="G15" s="150" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>  ***e.corp.in  </v>
       </c>
       <c r="H15" s="151"/>
@@ -9422,19 +9423,19 @@
         <v>111</v>
       </c>
       <c r="D16" s="149">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="E16" s="149" t="str">
+        <f t="shared" si="2"/>
+        <v>Not found</v>
+      </c>
+      <c r="F16" s="150" t="str">
         <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="E16" s="149" t="str">
-        <f t="shared" si="1"/>
-        <v>Not found</v>
-      </c>
-      <c r="F16" s="150" t="str">
+        <v>9315053957</v>
+      </c>
+      <c r="G16" s="150" t="str">
         <f t="shared" si="3"/>
-        <v>9527828713</v>
-      </c>
-      <c r="G16" s="150" t="str">
-        <f t="shared" si="2"/>
         <v>  ***son@company.io  </v>
       </c>
       <c r="H16" s="149"/>
@@ -9442,7 +9443,7 @@
         <v>259</v>
       </c>
       <c r="K16" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1" spans="1:15">
@@ -9456,24 +9457,24 @@
         <v>117</v>
       </c>
       <c r="D17" s="149">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="E17" s="149" t="str">
+        <f t="shared" si="2"/>
+        <v>Not found</v>
+      </c>
+      <c r="F17" s="150" t="str">
         <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="E17" s="149" t="str">
-        <f t="shared" si="1"/>
-        <v>Not found</v>
-      </c>
-      <c r="F17" s="150" t="str">
+        <v>9527828713</v>
+      </c>
+      <c r="G17" s="150" t="str">
         <f t="shared" si="3"/>
-        <v>9297208362</v>
-      </c>
-      <c r="G17" s="150" t="str">
-        <f t="shared" si="2"/>
         <v>  ***as@corp.in  </v>
       </c>
       <c r="H17" s="151"/>
       <c r="K17" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1" spans="1:15">
@@ -9487,24 +9488,24 @@
         <v>122</v>
       </c>
       <c r="D18" s="149">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="E18" s="149" t="str">
+        <f t="shared" si="2"/>
+        <v>Not found</v>
+      </c>
+      <c r="F18" s="150" t="str">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="E18" s="149" t="str">
-        <f t="shared" si="1"/>
-        <v>Not found</v>
-      </c>
-      <c r="F18" s="150" t="str">
+        <v>9297208362</v>
+      </c>
+      <c r="G18" s="150" t="str">
         <f t="shared" si="3"/>
-        <v>9803496718</v>
-      </c>
-      <c r="G18" s="150" t="str">
-        <f t="shared" si="2"/>
         <v>  ***rris@corp.in  </v>
       </c>
       <c r="H18" s="149"/>
       <c r="K18" s="155" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1" spans="1:15">
@@ -9518,16 +9519,19 @@
         <v>129</v>
       </c>
       <c r="D19" s="149">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="E19" s="149" t="str">
+        <f t="shared" si="2"/>
+        <v>Not found</v>
+      </c>
+      <c r="F19" s="150" t="str">
         <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="E19" s="149" t="str">
-        <f t="shared" si="1"/>
-        <v>Not found</v>
-      </c>
-      <c r="F19" s="150"/>
+        <v>9803496718</v>
+      </c>
       <c r="G19" s="150" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>  ***rk@biz.net  </v>
       </c>
       <c r="H19" s="151"/>
@@ -9543,16 +9547,19 @@
         <v>134</v>
       </c>
       <c r="D20" s="149">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="E20" s="149">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+      <c r="F20" s="150" t="str">
         <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="E20" s="149">
-        <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-      <c r="F20" s="150"/>
+        <v>9467638183</v>
+      </c>
       <c r="G20" s="150" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>  ***is@gmail.com  </v>
       </c>
       <c r="H20" s="149"/>
@@ -9568,16 +9575,19 @@
         <v>139</v>
       </c>
       <c r="D21" s="149">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="E21" s="149">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="F21" s="150" t="str">
         <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="E21" s="149">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="F21" s="150"/>
+        <v>9932782413</v>
+      </c>
       <c r="G21" s="150" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>  ***er@hotmail.com  </v>
       </c>
       <c r="H21" s="151"/>
@@ -9585,7 +9595,7 @@
         <v>258</v>
       </c>
       <c r="K21" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" spans="1:15">
@@ -9599,16 +9609,19 @@
         <v>144</v>
       </c>
       <c r="D22" s="149">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="E22" s="149">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+      <c r="F22" s="150" t="str">
         <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="E22" s="149">
-        <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-      <c r="F22" s="150"/>
+        <v>9480006467</v>
+      </c>
       <c r="G22" s="150" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>  ***@outlook.com  </v>
       </c>
       <c r="H22" s="149"/>
@@ -9616,16 +9629,16 @@
         <v>91</v>
       </c>
       <c r="L22" s="156" t="s">
+        <v>281</v>
+      </c>
+      <c r="M22" s="156" t="s">
+        <v>282</v>
+      </c>
+      <c r="N22" s="156" t="s">
+        <v>283</v>
+      </c>
+      <c r="O22" s="136" t="s">
         <v>284</v>
-      </c>
-      <c r="M22" s="156" t="s">
-        <v>285</v>
-      </c>
-      <c r="N22" s="156" t="s">
-        <v>286</v>
-      </c>
-      <c r="O22" s="136" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" spans="1:15">
@@ -9639,21 +9652,24 @@
         <v>149</v>
       </c>
       <c r="D23" s="149">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="E23" s="149">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+      <c r="F23" s="150" t="str">
         <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="E23" s="149">
-        <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-      <c r="F23" s="152"/>
+        <v>9633174470</v>
+      </c>
       <c r="G23" s="150" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>  ***@outlook.com  </v>
       </c>
       <c r="H23" s="151"/>
       <c r="K23" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" spans="1:15">
@@ -9667,16 +9683,19 @@
         <v>154</v>
       </c>
       <c r="D24" s="149">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="E24" s="149">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+      <c r="F24" s="150" t="str">
         <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="E24" s="149">
-        <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-      <c r="F24" s="150"/>
+        <v>9931124589</v>
+      </c>
       <c r="G24" s="150" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>  ***@outlook.com  </v>
       </c>
       <c r="H24" s="149"/>
@@ -9692,16 +9711,19 @@
         <v>159</v>
       </c>
       <c r="D25" s="149">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="E25" s="149" t="str">
+        <f t="shared" si="2"/>
+        <v>Not found</v>
+      </c>
+      <c r="F25" s="150" t="str">
         <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="E25" s="149" t="str">
-        <f t="shared" si="1"/>
-        <v>Not found</v>
-      </c>
-      <c r="F25" s="152"/>
+        <v>9232719732</v>
+      </c>
       <c r="G25" s="150" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>  ***ng@company.io  </v>
       </c>
       <c r="H25" s="151"/>
@@ -9717,16 +9739,19 @@
         <v>164</v>
       </c>
       <c r="D26" s="149">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="E26" s="149">
+        <f t="shared" si="2"/>
+        <v>21</v>
+      </c>
+      <c r="F26" s="150" t="str">
         <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="E26" s="149">
-        <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-      <c r="F26" s="150"/>
+        <v>9844781015</v>
+      </c>
       <c r="G26" s="150" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>  ***ght@outlook.com  </v>
       </c>
       <c r="H26" s="149"/>
@@ -9743,16 +9768,19 @@
         <v>169</v>
       </c>
       <c r="D27" s="149">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="E27" s="149">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+      <c r="F27" s="150" t="str">
         <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="E27" s="149">
-        <f t="shared" si="1"/>
-        <v>19</v>
-      </c>
-      <c r="F27" s="152"/>
+        <v>9566767798</v>
+      </c>
       <c r="G27" s="150" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>  ***pez@yahoo.com  </v>
       </c>
       <c r="H27" s="151"/>
@@ -9768,16 +9796,19 @@
         <v>174</v>
       </c>
       <c r="D28" s="149">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="E28" s="149" t="str">
+        <f t="shared" si="2"/>
+        <v>Not found</v>
+      </c>
+      <c r="F28" s="150" t="str">
         <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="E28" s="149" t="str">
-        <f t="shared" si="1"/>
-        <v>Not found</v>
-      </c>
-      <c r="F28" s="150"/>
+        <v>9579152218</v>
+      </c>
       <c r="G28" s="150" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>  ***@corp.in  </v>
       </c>
       <c r="H28" s="149"/>
@@ -9799,12 +9830,12 @@
     </row>
     <row r="31" ht="27.75" customHeight="1" spans="1:15">
       <c r="A31" s="158" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B31" s="158"/>
       <c r="C31" s="158"/>
       <c r="D31" s="107" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="E31" s="107"/>
       <c r="F31" s="107"/>
@@ -9812,12 +9843,12 @@
     </row>
     <row r="32" ht="27.75" customHeight="1" spans="1:15">
       <c r="A32" s="158" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B32" s="158"/>
       <c r="C32" s="158"/>
       <c r="D32" s="107" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="E32" s="107"/>
       <c r="F32" s="107"/>
@@ -9825,12 +9856,12 @@
     </row>
     <row r="33" ht="27.75" customHeight="1" spans="1:7">
       <c r="A33" s="158" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B33" s="158"/>
       <c r="C33" s="158"/>
       <c r="D33" s="107" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="E33" s="107"/>
       <c r="F33" s="107"/>
@@ -9838,12 +9869,12 @@
     </row>
     <row r="34" ht="27.75" customHeight="1" spans="1:7">
       <c r="A34" s="158" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B34" s="158"/>
       <c r="C34" s="158"/>
       <c r="D34" s="107" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="E34" s="107"/>
       <c r="F34" s="107"/>
@@ -9851,12 +9882,12 @@
     </row>
     <row r="35" ht="27.75" customHeight="1" spans="1:7">
       <c r="A35" s="158" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B35" s="158"/>
       <c r="C35" s="158"/>
       <c r="D35" s="107" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="E35" s="107"/>
       <c r="F35" s="107"/>
@@ -9864,12 +9895,12 @@
     </row>
     <row r="36" ht="27.75" customHeight="1" spans="1:7">
       <c r="A36" s="158" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B36" s="158"/>
       <c r="C36" s="158"/>
       <c r="D36" s="107" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E36" s="107"/>
       <c r="F36" s="107"/>
@@ -9877,12 +9908,12 @@
     </row>
     <row r="37" ht="27.75" customHeight="1" spans="1:7">
       <c r="A37" s="158" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B37" s="158"/>
       <c r="C37" s="158"/>
       <c r="D37" s="107" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="E37" s="107"/>
       <c r="F37" s="107"/>
@@ -9890,12 +9921,12 @@
     </row>
     <row r="38" ht="27.75" customHeight="1" spans="1:7">
       <c r="A38" s="158" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B38" s="158"/>
       <c r="C38" s="158"/>
       <c r="D38" s="107" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E38" s="107"/>
       <c r="F38" s="107"/>
@@ -9949,7 +9980,7 @@
   <sheetData>
     <row r="1" ht="37.5" customHeight="1" spans="1:8">
       <c r="A1" s="139" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B1" s="139"/>
       <c r="C1" s="139"/>
@@ -9961,7 +9992,7 @@
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:8">
       <c r="A2" s="140" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B2" s="140"/>
       <c r="C2" s="140"/>
@@ -9976,25 +10007,25 @@
         <v>2</v>
       </c>
       <c r="B3" s="141" t="s">
+        <v>304</v>
+      </c>
+      <c r="C3" s="141" t="s">
+        <v>305</v>
+      </c>
+      <c r="D3" s="141" t="s">
+        <v>306</v>
+      </c>
+      <c r="E3" s="141" t="s">
         <v>307</v>
       </c>
-      <c r="C3" s="141" t="s">
+      <c r="F3" s="141" t="s">
         <v>308</v>
       </c>
-      <c r="D3" s="141" t="s">
+      <c r="G3" s="141" t="s">
         <v>309</v>
       </c>
-      <c r="E3" s="141" t="s">
+      <c r="H3" s="141" t="s">
         <v>310</v>
-      </c>
-      <c r="F3" s="141" t="s">
-        <v>311</v>
-      </c>
-      <c r="G3" s="141" t="s">
-        <v>312</v>
-      </c>
-      <c r="H3" s="141" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1" spans="1:8">
@@ -10002,25 +10033,25 @@
         <v>17</v>
       </c>
       <c r="B4" s="142" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C4" s="142" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="D4" s="142" t="s">
         <v>18</v>
       </c>
       <c r="E4" s="142" t="s">
+        <v>313</v>
+      </c>
+      <c r="F4" s="142" t="s">
+        <v>314</v>
+      </c>
+      <c r="G4" s="142" t="s">
+        <v>315</v>
+      </c>
+      <c r="H4" s="142" t="s">
         <v>316</v>
-      </c>
-      <c r="F4" s="142" t="s">
-        <v>317</v>
-      </c>
-      <c r="G4" s="142" t="s">
-        <v>318</v>
-      </c>
-      <c r="H4" s="142" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" spans="1:8">
@@ -10028,25 +10059,25 @@
         <v>28</v>
       </c>
       <c r="B5" s="143" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C5" s="143" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="D5" s="143" t="s">
         <v>29</v>
       </c>
       <c r="E5" s="143" t="s">
+        <v>319</v>
+      </c>
+      <c r="F5" s="143" t="s">
+        <v>320</v>
+      </c>
+      <c r="G5" s="143" t="s">
+        <v>321</v>
+      </c>
+      <c r="H5" s="143" t="s">
         <v>322</v>
-      </c>
-      <c r="F5" s="143" t="s">
-        <v>323</v>
-      </c>
-      <c r="G5" s="143" t="s">
-        <v>324</v>
-      </c>
-      <c r="H5" s="143" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" spans="1:8">
@@ -10054,25 +10085,25 @@
         <v>37</v>
       </c>
       <c r="B6" s="142" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C6" s="142" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="D6" s="142" t="s">
         <v>229</v>
       </c>
       <c r="E6" s="142" t="s">
+        <v>325</v>
+      </c>
+      <c r="F6" s="142" t="s">
+        <v>326</v>
+      </c>
+      <c r="G6" s="142" t="s">
+        <v>327</v>
+      </c>
+      <c r="H6" s="142" t="s">
         <v>328</v>
-      </c>
-      <c r="F6" s="142" t="s">
-        <v>329</v>
-      </c>
-      <c r="G6" s="142" t="s">
-        <v>330</v>
-      </c>
-      <c r="H6" s="142" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="1:8">
@@ -10080,25 +10111,25 @@
         <v>45</v>
       </c>
       <c r="B7" s="143" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C7" s="143" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D7" s="143" t="s">
         <v>46</v>
       </c>
       <c r="E7" s="143" t="s">
+        <v>331</v>
+      </c>
+      <c r="F7" s="143" t="s">
+        <v>332</v>
+      </c>
+      <c r="G7" s="143" t="s">
+        <v>333</v>
+      </c>
+      <c r="H7" s="143" t="s">
         <v>334</v>
-      </c>
-      <c r="F7" s="143" t="s">
-        <v>335</v>
-      </c>
-      <c r="G7" s="143" t="s">
-        <v>336</v>
-      </c>
-      <c r="H7" s="143" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" spans="1:8">
@@ -10106,25 +10137,25 @@
         <v>54</v>
       </c>
       <c r="B8" s="142" t="s">
+        <v>335</v>
+      </c>
+      <c r="C8" s="142" t="s">
+        <v>336</v>
+      </c>
+      <c r="D8" s="142" t="s">
+        <v>337</v>
+      </c>
+      <c r="E8" s="142" t="s">
         <v>338</v>
       </c>
-      <c r="C8" s="142" t="s">
+      <c r="F8" s="142" t="s">
         <v>339</v>
       </c>
-      <c r="D8" s="142" t="s">
+      <c r="G8" s="142" t="s">
         <v>340</v>
       </c>
-      <c r="E8" s="142" t="s">
+      <c r="H8" s="142" t="s">
         <v>341</v>
-      </c>
-      <c r="F8" s="142" t="s">
-        <v>342</v>
-      </c>
-      <c r="G8" s="142" t="s">
-        <v>343</v>
-      </c>
-      <c r="H8" s="142" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" spans="1:8">
@@ -10802,12 +10833,12 @@
     </row>
     <row r="31" ht="27.75" customHeight="1" spans="1:8">
       <c r="A31" s="145" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B31" s="145"/>
       <c r="C31" s="145"/>
       <c r="D31" s="107" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="E31" s="107"/>
       <c r="F31" s="107"/>
@@ -10815,12 +10846,12 @@
     </row>
     <row r="32" ht="27.75" customHeight="1" spans="1:8">
       <c r="A32" s="145" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B32" s="145"/>
       <c r="C32" s="145"/>
       <c r="D32" s="107" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="E32" s="107"/>
       <c r="F32" s="107"/>
@@ -10828,12 +10859,12 @@
     </row>
     <row r="33" ht="27.75" customHeight="1" spans="1:7">
       <c r="A33" s="145" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B33" s="145"/>
       <c r="C33" s="145"/>
       <c r="D33" s="107" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E33" s="107"/>
       <c r="F33" s="107"/>
@@ -10841,12 +10872,12 @@
     </row>
     <row r="34" ht="27.75" customHeight="1" spans="1:7">
       <c r="A34" s="145" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B34" s="145"/>
       <c r="C34" s="145"/>
       <c r="D34" s="107" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="E34" s="107"/>
       <c r="F34" s="107"/>
@@ -10854,12 +10885,12 @@
     </row>
     <row r="35" ht="27.75" customHeight="1" spans="1:7">
       <c r="A35" s="145" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B35" s="145"/>
       <c r="C35" s="145"/>
       <c r="D35" s="107" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E35" s="107"/>
       <c r="F35" s="107"/>
@@ -10867,12 +10898,12 @@
     </row>
     <row r="36" ht="27.75" customHeight="1" spans="1:7">
       <c r="A36" s="145" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B36" s="145"/>
       <c r="C36" s="145"/>
       <c r="D36" s="107" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E36" s="107"/>
       <c r="F36" s="107"/>
@@ -10880,12 +10911,12 @@
     </row>
     <row r="37" ht="27.75" customHeight="1" spans="1:7">
       <c r="A37" s="145" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B37" s="145"/>
       <c r="C37" s="145"/>
       <c r="D37" s="107" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="E37" s="107"/>
       <c r="F37" s="107"/>
@@ -10893,12 +10924,12 @@
     </row>
     <row r="38" ht="27.75" customHeight="1" spans="1:7">
       <c r="A38" s="145" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B38" s="145"/>
       <c r="C38" s="145"/>
       <c r="D38" s="107" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E38" s="107"/>
       <c r="F38" s="107"/>
@@ -10906,117 +10937,117 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B45" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C45" t="s">
         <v>18</v>
       </c>
       <c r="D45" t="s">
+        <v>313</v>
+      </c>
+      <c r="E45" t="s">
+        <v>314</v>
+      </c>
+      <c r="F45" t="s">
+        <v>315</v>
+      </c>
+      <c r="G45" t="s">
         <v>316</v>
-      </c>
-      <c r="E45" t="s">
-        <v>317</v>
-      </c>
-      <c r="F45" t="s">
-        <v>318</v>
-      </c>
-      <c r="G45" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B46" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C46" t="s">
         <v>29</v>
       </c>
       <c r="D46" t="s">
+        <v>319</v>
+      </c>
+      <c r="E46" t="s">
+        <v>320</v>
+      </c>
+      <c r="F46" t="s">
+        <v>321</v>
+      </c>
+      <c r="G46" t="s">
         <v>322</v>
-      </c>
-      <c r="E46" t="s">
-        <v>323</v>
-      </c>
-      <c r="F46" t="s">
-        <v>324</v>
-      </c>
-      <c r="G46" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B47" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C47" t="s">
         <v>229</v>
       </c>
       <c r="D47" t="s">
+        <v>325</v>
+      </c>
+      <c r="E47" t="s">
+        <v>326</v>
+      </c>
+      <c r="F47" t="s">
+        <v>327</v>
+      </c>
+      <c r="G47" t="s">
         <v>328</v>
-      </c>
-      <c r="E47" t="s">
-        <v>329</v>
-      </c>
-      <c r="F47" t="s">
-        <v>330</v>
-      </c>
-      <c r="G47" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B48" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C48" t="s">
         <v>46</v>
       </c>
       <c r="D48" t="s">
+        <v>331</v>
+      </c>
+      <c r="E48" t="s">
+        <v>332</v>
+      </c>
+      <c r="F48" t="s">
+        <v>333</v>
+      </c>
+      <c r="G48" t="s">
         <v>334</v>
-      </c>
-      <c r="E48" t="s">
-        <v>335</v>
-      </c>
-      <c r="F48" t="s">
-        <v>336</v>
-      </c>
-      <c r="G48" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
+        <v>335</v>
+      </c>
+      <c r="B49" t="s">
+        <v>336</v>
+      </c>
+      <c r="C49" t="s">
+        <v>337</v>
+      </c>
+      <c r="D49" t="s">
         <v>338</v>
       </c>
-      <c r="B49" t="s">
+      <c r="E49" t="s">
         <v>339</v>
       </c>
-      <c r="C49" t="s">
+      <c r="F49" t="s">
         <v>340</v>
       </c>
-      <c r="D49" t="s">
+      <c r="G49" t="s">
         <v>341</v>
-      </c>
-      <c r="E49" t="s">
-        <v>342</v>
-      </c>
-      <c r="F49" t="s">
-        <v>343</v>
-      </c>
-      <c r="G49" t="s">
-        <v>344</v>
       </c>
     </row>
   </sheetData>
@@ -11067,7 +11098,7 @@
   <sheetData>
     <row r="1" ht="37.5" customHeight="1" spans="1:12">
       <c r="A1" s="127" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B1" s="127"/>
       <c r="C1" s="127"/>
@@ -11079,7 +11110,7 @@
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:12">
       <c r="A2" s="128" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B2" s="128"/>
       <c r="C2" s="128"/>
@@ -11097,22 +11128,22 @@
         <v>12</v>
       </c>
       <c r="C3" s="129" t="s">
+        <v>360</v>
+      </c>
+      <c r="D3" s="129" t="s">
+        <v>361</v>
+      </c>
+      <c r="E3" s="129" t="s">
+        <v>362</v>
+      </c>
+      <c r="F3" s="129" t="s">
         <v>363</v>
       </c>
-      <c r="D3" s="129" t="s">
+      <c r="G3" s="129" t="s">
         <v>364</v>
       </c>
-      <c r="E3" s="129" t="s">
+      <c r="H3" s="129" t="s">
         <v>365</v>
-      </c>
-      <c r="F3" s="129" t="s">
-        <v>366</v>
-      </c>
-      <c r="G3" s="129" t="s">
-        <v>367</v>
-      </c>
-      <c r="H3" s="129" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1" spans="1:12">
@@ -11138,7 +11169,7 @@
         <v>-1403</v>
       </c>
       <c r="H4" s="130" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" spans="1:12">
@@ -11164,7 +11195,7 @@
         <v>-845</v>
       </c>
       <c r="H5" s="133" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" spans="1:12">
@@ -11190,7 +11221,7 @@
         <v>-972</v>
       </c>
       <c r="H6" s="130" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="1:12">
@@ -11216,13 +11247,13 @@
         <v>-1051</v>
       </c>
       <c r="H7" s="133" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="K7" s="129" t="s">
+        <v>364</v>
+      </c>
+      <c r="L7" t="s">
         <v>367</v>
-      </c>
-      <c r="L7" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" spans="1:12">
@@ -11248,7 +11279,7 @@
         <v>-1094</v>
       </c>
       <c r="H8" s="130" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" spans="1:12">
@@ -11277,10 +11308,10 @@
         <v>25</v>
       </c>
       <c r="K9" s="129" t="s">
+        <v>365</v>
+      </c>
+      <c r="L9" t="s">
         <v>368</v>
-      </c>
-      <c r="L9" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" spans="1:12">
@@ -11306,10 +11337,10 @@
         <v>-956</v>
       </c>
       <c r="H10" s="130" t="s">
+        <v>366</v>
+      </c>
+      <c r="L10" s="136" t="s">
         <v>369</v>
-      </c>
-      <c r="L10" s="136" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" spans="1:12">
@@ -11335,10 +11366,10 @@
         <v>-822</v>
       </c>
       <c r="H11" s="133" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="L11" s="136" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1" spans="1:12">
@@ -11354,11 +11385,11 @@
       </c>
       <c r="D12" s="131">
         <f ca="1">TODAY()-'CRM Dataset'!K9</f>
-        <v>1177</v>
+        <v>1180</v>
       </c>
       <c r="E12" s="132">
         <f ca="1">NOW()</f>
-        <v>46258.5626851852</v>
+        <v>46261.5340972222</v>
       </c>
       <c r="F12" s="131">
         <f>DATE(2023,-6,-4)</f>
@@ -11373,7 +11404,7 @@
         <v>Expired</v>
       </c>
       <c r="L12" s="136" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1" spans="1:12">
@@ -11389,11 +11420,11 @@
       </c>
       <c r="D13" s="131">
         <f ca="1">TODAY()-'CRM Dataset'!K10</f>
-        <v>1550</v>
+        <v>1553</v>
       </c>
       <c r="E13" s="132">
         <f ca="1" t="shared" ref="E13:E22" si="0">NOW()</f>
-        <v>46258.5626851852</v>
+        <v>46261.5340972222</v>
       </c>
       <c r="F13" s="131">
         <f t="shared" ref="F13:F22" si="1">DATE(2023,-6,-4)</f>
@@ -11421,11 +11452,11 @@
       </c>
       <c r="D14" s="131">
         <f ca="1">TODAY()-'CRM Dataset'!K11</f>
-        <v>1653</v>
+        <v>1656</v>
       </c>
       <c r="E14" s="132">
         <f ca="1" t="shared" si="0"/>
-        <v>46258.5626851852</v>
+        <v>46261.5340972222</v>
       </c>
       <c r="F14" s="131">
         <f t="shared" si="1"/>
@@ -11454,11 +11485,11 @@
       </c>
       <c r="D15" s="131">
         <f ca="1">TODAY()-'CRM Dataset'!K12</f>
-        <v>1953</v>
+        <v>1956</v>
       </c>
       <c r="E15" s="132">
         <f ca="1" t="shared" si="0"/>
-        <v>46258.5626851852</v>
+        <v>46261.5340972222</v>
       </c>
       <c r="F15" s="131">
         <f t="shared" si="1"/>
@@ -11486,11 +11517,11 @@
       </c>
       <c r="D16" s="131">
         <f ca="1">TODAY()-'CRM Dataset'!K13</f>
-        <v>1254</v>
+        <v>1257</v>
       </c>
       <c r="E16" s="132">
         <f ca="1" t="shared" si="0"/>
-        <v>46258.5626851852</v>
+        <v>46261.5340972222</v>
       </c>
       <c r="F16" s="131">
         <f t="shared" si="1"/>
@@ -11518,11 +11549,11 @@
       </c>
       <c r="D17" s="131">
         <f ca="1">TODAY()-'CRM Dataset'!K14</f>
-        <v>1859</v>
+        <v>1862</v>
       </c>
       <c r="E17" s="132">
         <f ca="1" t="shared" si="0"/>
-        <v>46258.5626851852</v>
+        <v>46261.5340972222</v>
       </c>
       <c r="F17" s="131">
         <f t="shared" si="1"/>
@@ -11550,11 +11581,11 @@
       </c>
       <c r="D18" s="131">
         <f ca="1">TODAY()-'CRM Dataset'!K15</f>
-        <v>1517</v>
+        <v>1520</v>
       </c>
       <c r="E18" s="132">
         <f ca="1" t="shared" si="0"/>
-        <v>46258.5626851852</v>
+        <v>46261.5340972222</v>
       </c>
       <c r="F18" s="131">
         <f t="shared" si="1"/>
@@ -11582,11 +11613,11 @@
       </c>
       <c r="D19" s="131">
         <f ca="1">TODAY()-'CRM Dataset'!K16</f>
-        <v>1954</v>
+        <v>1957</v>
       </c>
       <c r="E19" s="132">
         <f ca="1" t="shared" si="0"/>
-        <v>46258.5626851852</v>
+        <v>46261.5340972222</v>
       </c>
       <c r="F19" s="131">
         <f t="shared" si="1"/>
@@ -11614,11 +11645,11 @@
       </c>
       <c r="D20" s="131">
         <f ca="1">TODAY()-'CRM Dataset'!K17</f>
-        <v>1790</v>
+        <v>1793</v>
       </c>
       <c r="E20" s="132">
         <f ca="1" t="shared" si="0"/>
-        <v>46258.5626851852</v>
+        <v>46261.5340972222</v>
       </c>
       <c r="F20" s="131">
         <f t="shared" si="1"/>
@@ -11646,11 +11677,11 @@
       </c>
       <c r="D21" s="131">
         <f ca="1">TODAY()-'CRM Dataset'!K18</f>
-        <v>1571</v>
+        <v>1574</v>
       </c>
       <c r="E21" s="132">
         <f ca="1" t="shared" si="0"/>
-        <v>46258.5626851852</v>
+        <v>46261.5340972222</v>
       </c>
       <c r="F21" s="131">
         <f t="shared" si="1"/>
@@ -11678,11 +11709,11 @@
       </c>
       <c r="D22" s="131">
         <f ca="1">TODAY()-'CRM Dataset'!K19</f>
-        <v>1478</v>
+        <v>1481</v>
       </c>
       <c r="E22" s="132">
         <f ca="1" t="shared" si="0"/>
-        <v>46258.5626851852</v>
+        <v>46261.5340972222</v>
       </c>
       <c r="F22" s="131">
         <f t="shared" si="1"/>
@@ -11710,11 +11741,11 @@
       </c>
       <c r="D23" s="131">
         <f ca="1">TODAY()-'CRM Dataset'!K20</f>
-        <v>1493</v>
+        <v>1496</v>
       </c>
       <c r="E23" s="132">
         <f ca="1" t="shared" ref="E23:E28" si="2">NOW()</f>
-        <v>46258.5626851852</v>
+        <v>46261.5340972222</v>
       </c>
       <c r="F23" s="131">
         <f t="shared" ref="F23:F28" si="3">DATE(2023,-6,-4)</f>
@@ -11742,11 +11773,11 @@
       </c>
       <c r="D24" s="131">
         <f ca="1">TODAY()-'CRM Dataset'!K21</f>
-        <v>1343</v>
+        <v>1346</v>
       </c>
       <c r="E24" s="132">
         <f ca="1" t="shared" si="2"/>
-        <v>46258.5626851852</v>
+        <v>46261.5340972222</v>
       </c>
       <c r="F24" s="131">
         <f t="shared" si="3"/>
@@ -11774,11 +11805,11 @@
       </c>
       <c r="D25" s="131">
         <f ca="1">TODAY()-'CRM Dataset'!K22</f>
-        <v>1327</v>
+        <v>1330</v>
       </c>
       <c r="E25" s="132">
         <f ca="1" t="shared" si="2"/>
-        <v>46258.5626851852</v>
+        <v>46261.5340972222</v>
       </c>
       <c r="F25" s="131">
         <f t="shared" si="3"/>
@@ -11806,11 +11837,11 @@
       </c>
       <c r="D26" s="131">
         <f ca="1">TODAY()-'CRM Dataset'!K23</f>
-        <v>1528</v>
+        <v>1531</v>
       </c>
       <c r="E26" s="132">
         <f ca="1" t="shared" si="2"/>
-        <v>46258.5626851852</v>
+        <v>46261.5340972222</v>
       </c>
       <c r="F26" s="131">
         <f t="shared" si="3"/>
@@ -11838,11 +11869,11 @@
       </c>
       <c r="D27" s="131">
         <f ca="1">TODAY()-'CRM Dataset'!K24</f>
-        <v>1802</v>
+        <v>1805</v>
       </c>
       <c r="E27" s="132">
         <f ca="1" t="shared" si="2"/>
-        <v>46258.5626851852</v>
+        <v>46261.5340972222</v>
       </c>
       <c r="F27" s="131">
         <f t="shared" si="3"/>
@@ -11870,11 +11901,11 @@
       </c>
       <c r="D28" s="131">
         <f ca="1">TODAY()-'CRM Dataset'!K25</f>
-        <v>1241</v>
+        <v>1244</v>
       </c>
       <c r="E28" s="132">
         <f ca="1" t="shared" si="2"/>
-        <v>46258.5626851852</v>
+        <v>46261.5340972222</v>
       </c>
       <c r="F28" s="131">
         <f t="shared" si="3"/>
@@ -11904,12 +11935,12 @@
     </row>
     <row r="31" ht="27.75" customHeight="1" spans="1:8">
       <c r="A31" s="138" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B31" s="138"/>
       <c r="C31" s="138"/>
       <c r="D31" s="107" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="E31" s="107"/>
       <c r="F31" s="107"/>
@@ -11917,12 +11948,12 @@
     </row>
     <row r="32" ht="27.75" customHeight="1" spans="1:8">
       <c r="A32" s="138" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B32" s="138"/>
       <c r="C32" s="138"/>
       <c r="D32" s="107" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="E32" s="107"/>
       <c r="F32" s="107"/>
@@ -11930,12 +11961,12 @@
     </row>
     <row r="33" ht="27.75" customHeight="1" spans="1:7">
       <c r="A33" s="138" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B33" s="138"/>
       <c r="C33" s="138"/>
       <c r="D33" s="107" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="E33" s="107"/>
       <c r="F33" s="107"/>
@@ -11943,12 +11974,12 @@
     </row>
     <row r="34" ht="27.75" customHeight="1" spans="1:7">
       <c r="A34" s="138" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B34" s="138"/>
       <c r="C34" s="138"/>
       <c r="D34" s="107" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="E34" s="107"/>
       <c r="F34" s="107"/>
@@ -11956,12 +11987,12 @@
     </row>
     <row r="35" ht="27.75" customHeight="1" spans="1:7">
       <c r="A35" s="138" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="B35" s="138"/>
       <c r="C35" s="138"/>
       <c r="D35" s="107" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="E35" s="107"/>
       <c r="F35" s="107"/>
@@ -11969,12 +12000,12 @@
     </row>
     <row r="36" ht="27.75" customHeight="1" spans="1:7">
       <c r="A36" s="138" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B36" s="138"/>
       <c r="C36" s="138"/>
       <c r="D36" s="107" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="E36" s="107"/>
       <c r="F36" s="107"/>
@@ -11982,12 +12013,12 @@
     </row>
     <row r="37" ht="27.75" customHeight="1" spans="1:7">
       <c r="A37" s="138" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B37" s="138"/>
       <c r="C37" s="138"/>
       <c r="D37" s="107" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="E37" s="107"/>
       <c r="F37" s="107"/>
@@ -11995,12 +12026,12 @@
     </row>
     <row r="38" ht="27.75" customHeight="1" spans="1:7">
       <c r="A38" s="138" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B38" s="138"/>
       <c r="C38" s="138"/>
       <c r="D38" s="107" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="E38" s="107"/>
       <c r="F38" s="107"/>
@@ -12052,7 +12083,7 @@
   <sheetData>
     <row r="1" ht="37.5" customHeight="1" spans="1:8">
       <c r="A1" s="120" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="B1" s="120"/>
       <c r="C1" s="120"/>
@@ -12064,7 +12095,7 @@
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:8">
       <c r="A2" s="121" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B2" s="121"/>
       <c r="C2" s="121"/>
@@ -12082,22 +12113,22 @@
         <v>12</v>
       </c>
       <c r="C3" s="122" t="s">
+        <v>390</v>
+      </c>
+      <c r="D3" s="122" t="s">
+        <v>391</v>
+      </c>
+      <c r="E3" s="122" t="s">
+        <v>392</v>
+      </c>
+      <c r="F3" s="122" t="s">
         <v>393</v>
       </c>
-      <c r="D3" s="122" t="s">
+      <c r="G3" s="122" t="s">
         <v>394</v>
       </c>
-      <c r="E3" s="122" t="s">
+      <c r="H3" s="122" t="s">
         <v>395</v>
-      </c>
-      <c r="F3" s="122" t="s">
-        <v>396</v>
-      </c>
-      <c r="G3" s="122" t="s">
-        <v>397</v>
-      </c>
-      <c r="H3" s="122" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1" spans="1:8">
@@ -12123,7 +12154,7 @@
         <v>37</v>
       </c>
       <c r="H4" s="123" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" spans="1:8">
@@ -12149,7 +12180,7 @@
         <v>49</v>
       </c>
       <c r="H5" s="124" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" spans="1:8">
@@ -12175,7 +12206,7 @@
         <v>27</v>
       </c>
       <c r="H6" s="123" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="1:8">
@@ -12201,7 +12232,7 @@
         <v>27</v>
       </c>
       <c r="H7" s="124" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" spans="1:8">
@@ -12891,12 +12922,12 @@
     </row>
     <row r="31" ht="27.75" customHeight="1" spans="1:8">
       <c r="A31" s="126" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B31" s="126"/>
       <c r="C31" s="126"/>
       <c r="D31" s="107" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="E31" s="107"/>
       <c r="F31" s="107"/>
@@ -12904,12 +12935,12 @@
     </row>
     <row r="32" ht="27.75" customHeight="1" spans="1:8">
       <c r="A32" s="126" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B32" s="126"/>
       <c r="C32" s="126"/>
       <c r="D32" s="107" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="E32" s="107"/>
       <c r="F32" s="107"/>
@@ -12917,12 +12948,12 @@
     </row>
     <row r="33" ht="27.75" customHeight="1" spans="1:7">
       <c r="A33" s="126" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B33" s="126"/>
       <c r="C33" s="126"/>
       <c r="D33" s="107" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="E33" s="107"/>
       <c r="F33" s="107"/>
@@ -12930,12 +12961,12 @@
     </row>
     <row r="34" ht="27.75" customHeight="1" spans="1:7">
       <c r="A34" s="126" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="B34" s="126"/>
       <c r="C34" s="126"/>
       <c r="D34" s="107" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="E34" s="107"/>
       <c r="F34" s="107"/>
@@ -12943,12 +12974,12 @@
     </row>
     <row r="35" ht="27.75" customHeight="1" spans="1:7">
       <c r="A35" s="126" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B35" s="126"/>
       <c r="C35" s="126"/>
       <c r="D35" s="107" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="E35" s="107"/>
       <c r="F35" s="107"/>
@@ -12956,12 +12987,12 @@
     </row>
     <row r="36" ht="27.75" customHeight="1" spans="1:7">
       <c r="A36" s="126" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="B36" s="126"/>
       <c r="C36" s="126"/>
       <c r="D36" s="107" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="E36" s="107"/>
       <c r="F36" s="107"/>
@@ -12969,12 +13000,12 @@
     </row>
     <row r="37" ht="27.75" customHeight="1" spans="1:7">
       <c r="A37" s="126" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B37" s="126"/>
       <c r="C37" s="126"/>
       <c r="D37" s="107" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="E37" s="107"/>
       <c r="F37" s="107"/>
@@ -12982,12 +13013,12 @@
     </row>
     <row r="38" ht="27.75" customHeight="1" spans="1:7">
       <c r="A38" s="126" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="B38" s="126"/>
       <c r="C38" s="126"/>
       <c r="D38" s="107" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="E38" s="107"/>
       <c r="F38" s="107"/>
@@ -13039,7 +13070,7 @@
   <sheetData>
     <row r="1" ht="37.5" customHeight="1" spans="1:8">
       <c r="A1" s="108" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B1" s="108"/>
       <c r="C1" s="108"/>
@@ -13051,7 +13082,7 @@
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:8">
       <c r="A2" s="109" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="B2" s="109"/>
       <c r="C2" s="109"/>
@@ -13072,19 +13103,19 @@
         <v>13</v>
       </c>
       <c r="D3" s="110" t="s">
+        <v>417</v>
+      </c>
+      <c r="E3" s="110" t="s">
+        <v>418</v>
+      </c>
+      <c r="F3" s="110" t="s">
+        <v>419</v>
+      </c>
+      <c r="G3" s="110" t="s">
         <v>420</v>
       </c>
-      <c r="E3" s="110" t="s">
+      <c r="H3" s="111" t="s">
         <v>421</v>
-      </c>
-      <c r="F3" s="110" t="s">
-        <v>422</v>
-      </c>
-      <c r="G3" s="110" t="s">
-        <v>423</v>
-      </c>
-      <c r="H3" s="111" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1" spans="1:8">
@@ -13852,12 +13883,12 @@
     </row>
     <row r="31" ht="27.75" customHeight="1" spans="1:8">
       <c r="A31" s="119" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B31" s="119"/>
       <c r="C31" s="119"/>
       <c r="D31" s="107" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E31" s="107"/>
       <c r="F31" s="107"/>
@@ -13865,12 +13896,12 @@
     </row>
     <row r="32" ht="27.75" customHeight="1" spans="1:8">
       <c r="A32" s="119" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="B32" s="119"/>
       <c r="C32" s="119"/>
       <c r="D32" s="107" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="E32" s="107"/>
       <c r="F32" s="107"/>
@@ -13878,12 +13909,12 @@
     </row>
     <row r="33" ht="27.75" customHeight="1" spans="1:7">
       <c r="A33" s="119" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B33" s="119"/>
       <c r="C33" s="119"/>
       <c r="D33" s="107" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E33" s="107"/>
       <c r="F33" s="107"/>
@@ -13891,12 +13922,12 @@
     </row>
     <row r="34" ht="27.75" customHeight="1" spans="1:7">
       <c r="A34" s="119" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B34" s="119"/>
       <c r="C34" s="119"/>
       <c r="D34" s="107" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="E34" s="107"/>
       <c r="F34" s="107"/>
@@ -13904,12 +13935,12 @@
     </row>
     <row r="35" ht="27.75" customHeight="1" spans="1:7">
       <c r="A35" s="119" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="B35" s="119"/>
       <c r="C35" s="119"/>
       <c r="D35" s="107" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E35" s="107"/>
       <c r="F35" s="107"/>
@@ -13917,12 +13948,12 @@
     </row>
     <row r="36" ht="27.75" customHeight="1" spans="1:7">
       <c r="A36" s="119" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="B36" s="119"/>
       <c r="C36" s="119"/>
       <c r="D36" s="107" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="E36" s="107"/>
       <c r="F36" s="107"/>
@@ -13930,12 +13961,12 @@
     </row>
     <row r="37" ht="27.75" customHeight="1" spans="1:7">
       <c r="A37" s="119" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="B37" s="119"/>
       <c r="C37" s="119"/>
       <c r="D37" s="107" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E37" s="107"/>
       <c r="F37" s="107"/>
@@ -13943,12 +13974,12 @@
     </row>
     <row r="38" ht="27.75" customHeight="1" spans="1:7">
       <c r="A38" s="119" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B38" s="119"/>
       <c r="C38" s="119"/>
       <c r="D38" s="107" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="E38" s="107"/>
       <c r="F38" s="107"/>
@@ -14001,7 +14032,7 @@
   <sheetData>
     <row r="1" ht="37.5" customHeight="1" spans="1:12">
       <c r="A1" s="95" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="B1" s="95"/>
       <c r="C1" s="95"/>
@@ -14013,7 +14044,7 @@
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:12">
       <c r="A2" s="96" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="B2" s="96"/>
       <c r="C2" s="96"/>
@@ -14028,25 +14059,25 @@
         <v>2</v>
       </c>
       <c r="B3" s="97" t="s">
+        <v>440</v>
+      </c>
+      <c r="C3" s="97" t="s">
+        <v>441</v>
+      </c>
+      <c r="D3" s="97" t="s">
+        <v>442</v>
+      </c>
+      <c r="E3" s="97" t="s">
         <v>443</v>
       </c>
-      <c r="C3" s="97" t="s">
+      <c r="F3" s="97" t="s">
         <v>444</v>
       </c>
-      <c r="D3" s="97" t="s">
+      <c r="G3" s="97" t="s">
         <v>445</v>
       </c>
-      <c r="E3" s="97" t="s">
+      <c r="H3" s="97" t="s">
         <v>446</v>
-      </c>
-      <c r="F3" s="97" t="s">
-        <v>447</v>
-      </c>
-      <c r="G3" s="97" t="s">
-        <v>448</v>
-      </c>
-      <c r="H3" s="97" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1" spans="1:12">
@@ -14073,7 +14104,7 @@
         <v>Afternoon</v>
       </c>
       <c r="H4" s="100" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" spans="1:12">
@@ -14100,7 +14131,7 @@
         <v>Afternoon</v>
       </c>
       <c r="H5" s="104" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" spans="1:12">
@@ -14127,7 +14158,7 @@
         <v>Evening</v>
       </c>
       <c r="H6" s="100" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="1:12">
@@ -14154,7 +14185,7 @@
         <v>Evening</v>
       </c>
       <c r="H7" s="104" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" spans="1:12">
@@ -14181,13 +14212,13 @@
         <v>Evening</v>
       </c>
       <c r="H8" s="100" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="K8" s="97" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="L8" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" spans="1:12">
@@ -14788,12 +14819,12 @@
     </row>
     <row r="31" ht="27.75" customHeight="1" spans="1:8">
       <c r="A31" s="106" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B31" s="106"/>
       <c r="C31" s="106"/>
       <c r="D31" s="107" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="E31" s="107"/>
       <c r="F31" s="107"/>
@@ -14801,12 +14832,12 @@
     </row>
     <row r="32" ht="27.75" customHeight="1" spans="1:8">
       <c r="A32" s="106" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="B32" s="106"/>
       <c r="C32" s="106"/>
       <c r="D32" s="107" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="E32" s="107"/>
       <c r="F32" s="107"/>
@@ -14814,12 +14845,12 @@
     </row>
     <row r="33" ht="27.75" customHeight="1" spans="1:7">
       <c r="A33" s="106" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="B33" s="106"/>
       <c r="C33" s="106"/>
       <c r="D33" s="107" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="E33" s="107"/>
       <c r="F33" s="107"/>
@@ -14827,12 +14858,12 @@
     </row>
     <row r="34" ht="27.75" customHeight="1" spans="1:7">
       <c r="A34" s="106" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="B34" s="106"/>
       <c r="C34" s="106"/>
       <c r="D34" s="107" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="E34" s="107"/>
       <c r="F34" s="107"/>
@@ -14840,12 +14871,12 @@
     </row>
     <row r="35" ht="27.75" customHeight="1" spans="1:7">
       <c r="A35" s="106" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="B35" s="106"/>
       <c r="C35" s="106"/>
       <c r="D35" s="107" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="E35" s="107"/>
       <c r="F35" s="107"/>
@@ -14853,12 +14884,12 @@
     </row>
     <row r="36" ht="27.75" customHeight="1" spans="1:7">
       <c r="A36" s="106" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="B36" s="106"/>
       <c r="C36" s="106"/>
       <c r="D36" s="107" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="E36" s="107"/>
       <c r="F36" s="107"/>
@@ -14866,12 +14897,12 @@
     </row>
     <row r="37" ht="27.75" customHeight="1" spans="1:7">
       <c r="A37" s="106" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B37" s="106"/>
       <c r="C37" s="106"/>
       <c r="D37" s="107" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="E37" s="107"/>
       <c r="F37" s="107"/>
@@ -14879,12 +14910,12 @@
     </row>
     <row r="38" ht="27.75" customHeight="1" spans="1:7">
       <c r="A38" s="106" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="B38" s="106"/>
       <c r="C38" s="106"/>
       <c r="D38" s="107" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="E38" s="107"/>
       <c r="F38" s="107"/>

--- a/Lab/Excel_Text_Date_Functions - assignment.xlsx
+++ b/Lab/Excel_Text_Date_Functions - assignment.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6800" tabRatio="500" firstSheet="3" activeTab="3"/>
+    <workbookView windowWidth="19200" windowHeight="6800" tabRatio="500" firstSheet="5" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="CRM Dataset" sheetId="1" r:id="rId1"/>
@@ -9188,8 +9188,8 @@
         <v>9762918409</v>
       </c>
       <c r="G8" s="150" t="str">
-        <f>SUBSTITUTE(C8,LEFT(TRIM(C8),9),"***")</f>
-        <v>  ***@company.io  </v>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8,LEFT(TRIM(C8),9),"***"),".",)," ","")</f>
+        <v>***@companyio</v>
       </c>
       <c r="H8" s="149" t="s">
         <v>269</v>
@@ -9221,8 +9221,8 @@
         <v>9159933789</v>
       </c>
       <c r="G9" s="150" t="str">
-        <f t="shared" ref="G9:G28" si="3">SUBSTITUTE(C9,LEFT(TRIM(C9),9),"***")</f>
-        <v>  ***@webmail.com  </v>
+        <f t="shared" ref="G9:G28" si="3">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9,LEFT(TRIM(C9),9),"***"),".",)," ","")</f>
+        <v>***@webmailcom</v>
       </c>
       <c r="H9" s="151"/>
     </row>
@@ -9250,7 +9250,7 @@
       </c>
       <c r="G10" s="150" t="str">
         <f t="shared" si="3"/>
-        <v>  ***@hotmail.com  </v>
+        <v>***@hotmailcom</v>
       </c>
       <c r="H10" s="149"/>
       <c r="J10" s="148" t="s">
@@ -9284,7 +9284,7 @@
       </c>
       <c r="G11" s="150" t="str">
         <f t="shared" si="3"/>
-        <v>  ***is#corp.in  </v>
+        <v>***is#corpin</v>
       </c>
       <c r="H11" s="151"/>
       <c r="K11" t="s">
@@ -9315,7 +9315,7 @@
       </c>
       <c r="G12" s="150" t="str">
         <f t="shared" si="3"/>
-        <v>  ***in@hotmail.com  </v>
+        <v>***in@hotmailcom</v>
       </c>
       <c r="H12" s="149"/>
     </row>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="G13" s="150" t="str">
         <f t="shared" si="3"/>
-        <v>  ***on@company.io  </v>
+        <v>***on@companyio</v>
       </c>
       <c r="H13" s="151"/>
       <c r="J13" s="148" t="s">
@@ -9377,7 +9377,7 @@
       </c>
       <c r="G14" s="150" t="str">
         <f t="shared" si="3"/>
-        <v>  ***lor@webmail.com  </v>
+        <v>***lor@webmailcom</v>
       </c>
       <c r="H14" s="149"/>
       <c r="K14" t="s">
@@ -9408,7 +9408,7 @@
       </c>
       <c r="G15" s="150" t="str">
         <f t="shared" si="3"/>
-        <v>  ***e.corp.in  </v>
+        <v>***ecorpin</v>
       </c>
       <c r="H15" s="151"/>
     </row>
@@ -9436,7 +9436,7 @@
       </c>
       <c r="G16" s="150" t="str">
         <f t="shared" si="3"/>
-        <v>  ***son@company.io  </v>
+        <v>***son@companyio</v>
       </c>
       <c r="H16" s="149"/>
       <c r="J16" s="148" t="s">
@@ -9470,7 +9470,7 @@
       </c>
       <c r="G17" s="150" t="str">
         <f t="shared" si="3"/>
-        <v>  ***as@corp.in  </v>
+        <v>***as@corpin</v>
       </c>
       <c r="H17" s="151"/>
       <c r="K17" t="s">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="G18" s="150" t="str">
         <f t="shared" si="3"/>
-        <v>  ***rris@corp.in  </v>
+        <v>***rris@corpin</v>
       </c>
       <c r="H18" s="149"/>
       <c r="K18" s="155" t="s">
@@ -9532,7 +9532,7 @@
       </c>
       <c r="G19" s="150" t="str">
         <f t="shared" si="3"/>
-        <v>  ***rk@biz.net  </v>
+        <v>***rk@biznet</v>
       </c>
       <c r="H19" s="151"/>
     </row>
@@ -9560,7 +9560,7 @@
       </c>
       <c r="G20" s="150" t="str">
         <f t="shared" si="3"/>
-        <v>  ***is@gmail.com  </v>
+        <v>***is@gmailcom</v>
       </c>
       <c r="H20" s="149"/>
     </row>
@@ -9588,7 +9588,7 @@
       </c>
       <c r="G21" s="150" t="str">
         <f t="shared" si="3"/>
-        <v>  ***er@hotmail.com  </v>
+        <v>***er@hotmailcom</v>
       </c>
       <c r="H21" s="151"/>
       <c r="J21" s="148" t="s">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="G22" s="150" t="str">
         <f t="shared" si="3"/>
-        <v>  ***@outlook.com  </v>
+        <v>***@outlookcom</v>
       </c>
       <c r="H22" s="149"/>
       <c r="K22" s="156">
@@ -9665,7 +9665,7 @@
       </c>
       <c r="G23" s="150" t="str">
         <f t="shared" si="3"/>
-        <v>  ***@outlook.com  </v>
+        <v>***@outlookcom</v>
       </c>
       <c r="H23" s="151"/>
       <c r="K23" t="s">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="G24" s="150" t="str">
         <f t="shared" si="3"/>
-        <v>  ***@outlook.com  </v>
+        <v>***@outlookcom</v>
       </c>
       <c r="H24" s="149"/>
     </row>
@@ -9724,7 +9724,7 @@
       </c>
       <c r="G25" s="150" t="str">
         <f t="shared" si="3"/>
-        <v>  ***ng@company.io  </v>
+        <v>***ng@companyio</v>
       </c>
       <c r="H25" s="151"/>
     </row>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="G26" s="150" t="str">
         <f t="shared" si="3"/>
-        <v>  ***ght@outlook.com  </v>
+        <v>***ght@outlookcom</v>
       </c>
       <c r="H26" s="149"/>
       <c r="K26" s="136"/>
@@ -9781,7 +9781,7 @@
       </c>
       <c r="G27" s="150" t="str">
         <f t="shared" si="3"/>
-        <v>  ***pez@yahoo.com  </v>
+        <v>***pez@yahoocom</v>
       </c>
       <c r="H27" s="151"/>
     </row>
@@ -9809,7 +9809,7 @@
       </c>
       <c r="G28" s="150" t="str">
         <f t="shared" si="3"/>
-        <v>  ***@corp.in  </v>
+        <v>***@corpin</v>
       </c>
       <c r="H28" s="149"/>
       <c r="K28" s="136"/>
@@ -11385,11 +11385,11 @@
       </c>
       <c r="D12" s="131">
         <f ca="1">TODAY()-'CRM Dataset'!K9</f>
-        <v>1180</v>
+        <v>1185</v>
       </c>
       <c r="E12" s="132">
         <f ca="1">NOW()</f>
-        <v>46261.5340972222</v>
+        <v>46266.929375</v>
       </c>
       <c r="F12" s="131">
         <f>DATE(2023,-6,-4)</f>
@@ -11420,11 +11420,11 @@
       </c>
       <c r="D13" s="131">
         <f ca="1">TODAY()-'CRM Dataset'!K10</f>
-        <v>1553</v>
+        <v>1558</v>
       </c>
       <c r="E13" s="132">
         <f ca="1" t="shared" ref="E13:E22" si="0">NOW()</f>
-        <v>46261.5340972222</v>
+        <v>46266.929375</v>
       </c>
       <c r="F13" s="131">
         <f t="shared" ref="F13:F22" si="1">DATE(2023,-6,-4)</f>
@@ -11452,11 +11452,11 @@
       </c>
       <c r="D14" s="131">
         <f ca="1">TODAY()-'CRM Dataset'!K11</f>
-        <v>1656</v>
+        <v>1661</v>
       </c>
       <c r="E14" s="132">
         <f ca="1" t="shared" si="0"/>
-        <v>46261.5340972222</v>
+        <v>46266.929375</v>
       </c>
       <c r="F14" s="131">
         <f t="shared" si="1"/>
@@ -11485,11 +11485,11 @@
       </c>
       <c r="D15" s="131">
         <f ca="1">TODAY()-'CRM Dataset'!K12</f>
-        <v>1956</v>
+        <v>1961</v>
       </c>
       <c r="E15" s="132">
         <f ca="1" t="shared" si="0"/>
-        <v>46261.5340972222</v>
+        <v>46266.929375</v>
       </c>
       <c r="F15" s="131">
         <f t="shared" si="1"/>
@@ -11517,11 +11517,11 @@
       </c>
       <c r="D16" s="131">
         <f ca="1">TODAY()-'CRM Dataset'!K13</f>
-        <v>1257</v>
+        <v>1262</v>
       </c>
       <c r="E16" s="132">
         <f ca="1" t="shared" si="0"/>
-        <v>46261.5340972222</v>
+        <v>46266.929375</v>
       </c>
       <c r="F16" s="131">
         <f t="shared" si="1"/>
@@ -11549,11 +11549,11 @@
       </c>
       <c r="D17" s="131">
         <f ca="1">TODAY()-'CRM Dataset'!K14</f>
-        <v>1862</v>
+        <v>1867</v>
       </c>
       <c r="E17" s="132">
         <f ca="1" t="shared" si="0"/>
-        <v>46261.5340972222</v>
+        <v>46266.929375</v>
       </c>
       <c r="F17" s="131">
         <f t="shared" si="1"/>
@@ -11581,11 +11581,11 @@
       </c>
       <c r="D18" s="131">
         <f ca="1">TODAY()-'CRM Dataset'!K15</f>
-        <v>1520</v>
+        <v>1525</v>
       </c>
       <c r="E18" s="132">
         <f ca="1" t="shared" si="0"/>
-        <v>46261.5340972222</v>
+        <v>46266.929375</v>
       </c>
       <c r="F18" s="131">
         <f t="shared" si="1"/>
@@ -11613,11 +11613,11 @@
       </c>
       <c r="D19" s="131">
         <f ca="1">TODAY()-'CRM Dataset'!K16</f>
-        <v>1957</v>
+        <v>1962</v>
       </c>
       <c r="E19" s="132">
         <f ca="1" t="shared" si="0"/>
-        <v>46261.5340972222</v>
+        <v>46266.929375</v>
       </c>
       <c r="F19" s="131">
         <f t="shared" si="1"/>
@@ -11645,11 +11645,11 @@
       </c>
       <c r="D20" s="131">
         <f ca="1">TODAY()-'CRM Dataset'!K17</f>
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="E20" s="132">
         <f ca="1" t="shared" si="0"/>
-        <v>46261.5340972222</v>
+        <v>46266.929375</v>
       </c>
       <c r="F20" s="131">
         <f t="shared" si="1"/>
@@ -11677,11 +11677,11 @@
       </c>
       <c r="D21" s="131">
         <f ca="1">TODAY()-'CRM Dataset'!K18</f>
-        <v>1574</v>
+        <v>1579</v>
       </c>
       <c r="E21" s="132">
         <f ca="1" t="shared" si="0"/>
-        <v>46261.5340972222</v>
+        <v>46266.929375</v>
       </c>
       <c r="F21" s="131">
         <f t="shared" si="1"/>
@@ -11709,11 +11709,11 @@
       </c>
       <c r="D22" s="131">
         <f ca="1">TODAY()-'CRM Dataset'!K19</f>
-        <v>1481</v>
+        <v>1486</v>
       </c>
       <c r="E22" s="132">
         <f ca="1" t="shared" si="0"/>
-        <v>46261.5340972222</v>
+        <v>46266.929375</v>
       </c>
       <c r="F22" s="131">
         <f t="shared" si="1"/>
@@ -11741,11 +11741,11 @@
       </c>
       <c r="D23" s="131">
         <f ca="1">TODAY()-'CRM Dataset'!K20</f>
-        <v>1496</v>
+        <v>1501</v>
       </c>
       <c r="E23" s="132">
         <f ca="1" t="shared" ref="E23:E28" si="2">NOW()</f>
-        <v>46261.5340972222</v>
+        <v>46266.929375</v>
       </c>
       <c r="F23" s="131">
         <f t="shared" ref="F23:F28" si="3">DATE(2023,-6,-4)</f>
@@ -11773,11 +11773,11 @@
       </c>
       <c r="D24" s="131">
         <f ca="1">TODAY()-'CRM Dataset'!K21</f>
-        <v>1346</v>
+        <v>1351</v>
       </c>
       <c r="E24" s="132">
         <f ca="1" t="shared" si="2"/>
-        <v>46261.5340972222</v>
+        <v>46266.929375</v>
       </c>
       <c r="F24" s="131">
         <f t="shared" si="3"/>
@@ -11805,11 +11805,11 @@
       </c>
       <c r="D25" s="131">
         <f ca="1">TODAY()-'CRM Dataset'!K22</f>
-        <v>1330</v>
+        <v>1335</v>
       </c>
       <c r="E25" s="132">
         <f ca="1" t="shared" si="2"/>
-        <v>46261.5340972222</v>
+        <v>46266.929375</v>
       </c>
       <c r="F25" s="131">
         <f t="shared" si="3"/>
@@ -11837,11 +11837,11 @@
       </c>
       <c r="D26" s="131">
         <f ca="1">TODAY()-'CRM Dataset'!K23</f>
-        <v>1531</v>
+        <v>1536</v>
       </c>
       <c r="E26" s="132">
         <f ca="1" t="shared" si="2"/>
-        <v>46261.5340972222</v>
+        <v>46266.929375</v>
       </c>
       <c r="F26" s="131">
         <f t="shared" si="3"/>
@@ -11869,11 +11869,11 @@
       </c>
       <c r="D27" s="131">
         <f ca="1">TODAY()-'CRM Dataset'!K24</f>
-        <v>1805</v>
+        <v>1810</v>
       </c>
       <c r="E27" s="132">
         <f ca="1" t="shared" si="2"/>
-        <v>46261.5340972222</v>
+        <v>46266.929375</v>
       </c>
       <c r="F27" s="131">
         <f t="shared" si="3"/>
@@ -11901,11 +11901,11 @@
       </c>
       <c r="D28" s="131">
         <f ca="1">TODAY()-'CRM Dataset'!K25</f>
-        <v>1244</v>
+        <v>1249</v>
       </c>
       <c r="E28" s="132">
         <f ca="1" t="shared" si="2"/>
-        <v>46261.5340972222</v>
+        <v>46266.929375</v>
       </c>
       <c r="F28" s="131">
         <f t="shared" si="3"/>
